--- a/servers/maze_main_server/conf.d/data/maze_save_brush_monsters_v8【迷宫-救援敌人-刷怪】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_brush_monsters_v8【迷宫-救援敌人-刷怪】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8975DAB-70C9-4849-978C-A4556503BFF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB55149-613C-4719-B93B-2C947EDCAB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -70,10 +70,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,1,2,1,2,1,1,3,1,1,4,3,1,1,2,1,3,2,2,4,2,2,3,2,3,3,2,3,4,2,3,4,4</t>
-  </si>
-  <si>
-    <t>1000,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200,3200</t>
+    <t>1,1,2,1,2,1,1,3,1,1,4,3,1,1,2,1,1,2,1,4,2,1,3,2,3,3,2,3,4,2</t>
+  </si>
+  <si>
+    <t>1000,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400</t>
+  </si>
+  <si>
+    <t>1,1,2,1,2,1,2,3,1,2,4,3,1,1,2,1,4,2,1,4,2,1,3,2,3,3,2,3,4,2</t>
+  </si>
+  <si>
+    <t>2,2,3,2,3,4,4</t>
+  </si>
+  <si>
+    <t>1000,3000,3000,3000,3000,3000,3000</t>
   </si>
 </sst>
 </file>
@@ -510,7 +519,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>9</v>
@@ -521,10 +530,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_save_brush_monsters_v8【迷宫-救援敌人-刷怪】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_save_brush_monsters_v8【迷宫-救援敌人-刷怪】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB55149-613C-4719-B93B-2C947EDCAB19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE985947-ADFE-4575-B7FB-AB55CBAAD7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>paipaiworld_config</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -70,9 +70,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,1,2,1,2,1,1,3,1,1,4,3,1,1,2,1,1,2,1,4,2,1,3,2,3,3,2,3,4,2</t>
-  </si>
-  <si>
     <t>1000,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400,3400</t>
   </si>
   <si>
@@ -83,6 +80,12 @@
   </si>
   <si>
     <t>1000,3000,3000,3000,3000,3000,3000</t>
+  </si>
+  <si>
+    <t>1,2,2,1,2,1,3,1,2,1,4,3,1,2,4</t>
+  </si>
+  <si>
+    <t>1000,7000,7000,7000,7000,7000,7000,7000,7000,7000,7000,7000,7000,7000,7000</t>
   </si>
 </sst>
 </file>
@@ -508,10 +511,10 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.15">
@@ -519,10 +522,10 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.15">
@@ -530,10 +533,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>12</v>
       </c>
     </row>
   </sheetData>
